--- a/examples/sequence/OUL/result/features.xlsx
+++ b/examples/sequence/OUL/result/features.xlsx
@@ -791,34 +791,34 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.9</v>
       </c>
-      <c r="D10" t="n">
+      <c r="J10" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="E10" t="n">
+      <c r="K10" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="F10" t="n">
+      <c r="L10" t="n">
         <v>1.066666666666667</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">

--- a/examples/sequence/OUL/result/features.xlsx
+++ b/examples/sequence/OUL/result/features.xlsx
@@ -560,37 +560,37 @@
         <v>116</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>16.9</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>13.03333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3.733333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -598,37 +598,37 @@
         <v>117</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7.066666666666666</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.433333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.233333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -636,34 +636,34 @@
         <v>118</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>53.93333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>21.56666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>18.26666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -674,37 +674,37 @@
         <v>119</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>15.86666666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>8.233333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>9.633333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.433333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -712,37 +712,37 @@
         <v>120</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>34.46666666666667</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>18.43333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3.733333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.433333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -750,37 +750,37 @@
         <v>121</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>26.6</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>4.133333333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -788,34 +788,34 @@
         <v>136</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>22.36666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5.766666666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.233333333333333</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>1.433333333333333</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.066666666666667</v>
@@ -826,13 +826,13 @@
         <v>137</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>6.266666666666667</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -841,19 +841,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -864,37 +864,37 @@
         <v>160</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.566666666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4.133333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2.733333333333333</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -902,22 +902,22 @@
         <v>161</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>5.366666666666666</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -940,31 +940,31 @@
         <v>162</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3.433333333333333</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>7.366666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3.633333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.633333333333333</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -978,34 +978,34 @@
         <v>163</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         <v>206</v>
       </c>
       <c r="B16" t="n">
-        <v>26.83333333333333</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="C16" t="n">
-        <v>16.86666666666667</v>
+        <v>13.5</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9</v>
+        <v>6.266666666666667</v>
       </c>
       <c r="E16" t="n">
         <v>2.333333333333333</v>
@@ -1054,37 +1054,37 @@
         <v>207</v>
       </c>
       <c r="B17" t="n">
-        <v>18.83333333333333</v>
+        <v>18.4</v>
       </c>
       <c r="C17" t="n">
-        <v>9.966666666666667</v>
+        <v>9.6</v>
       </c>
       <c r="D17" t="n">
-        <v>4.866666666666666</v>
+        <v>6.1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.233333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="F17" t="n">
         <v>0.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>9.5</v>
+        <v>7.633333333333334</v>
       </c>
       <c r="I17" t="n">
+        <v>2.233333333333333</v>
+      </c>
+      <c r="J17" t="n">
         <v>2.533333333333333</v>
       </c>
-      <c r="J17" t="n">
-        <v>2.766666666666667</v>
-      </c>
       <c r="K17" t="n">
-        <v>1.966666666666667</v>
+        <v>1.2</v>
       </c>
       <c r="L17" t="n">
-        <v>2.8</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -1092,37 +1092,37 @@
         <v>210</v>
       </c>
       <c r="B18" t="n">
-        <v>41.63333333333333</v>
+        <v>34.93333333333333</v>
       </c>
       <c r="C18" t="n">
-        <v>22.33333333333333</v>
+        <v>22.96666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>14.9</v>
+        <v>15.13333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>18.16666666666667</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>5.366666666666666</v>
+        <v>6.433333333333334</v>
       </c>
       <c r="G18" t="n">
-        <v>9.1</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="H18" t="n">
-        <v>22.16666666666667</v>
+        <v>19.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1.666666666666667</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>3.766666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>8.233333333333333</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2.666666666666667</v>
       </c>
     </row>
     <row r="19">
@@ -1130,19 +1130,19 @@
         <v>211</v>
       </c>
       <c r="B19" t="n">
-        <v>3.6</v>
+        <v>4.966666666666667</v>
       </c>
       <c r="C19" t="n">
-        <v>2.5</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.966666666666667</v>
       </c>
       <c r="E19" t="n">
-        <v>1.166666666666667</v>
+        <v>2.266666666666667</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1154,7 +1154,7 @@
         <v>0.6333333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
         <v>1.166666666666667</v>
